--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-adverse-event-document.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-adverse-event-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -651,28 +651,28 @@
     <t>AdverseEvent.seriousness</t>
   </si>
   <si>
+    <t>Seriousness of the event</t>
+  </si>
+  <si>
+    <t>Assessment whether this event was of real importance.</t>
+  </si>
+  <si>
+    <t>Overall seriousness of this event for the patient.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/adverse-event-seriousness|4.0.1</t>
+  </si>
+  <si>
+    <t>AdverseEvent.severity</t>
+  </si>
+  <si>
     <t>Gravité de l'effet indésirable</t>
   </si>
   <si>
-    <t>Assessment whether this event was of real importance.</t>
+    <t>Describes the severity of the adverse event, in relation to the subject. Contrast to AdverseEvent.seriousness - a severe rash might not be serious, but a mild heart problem is.</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-gravite-cisis</t>
-  </si>
-  <si>
-    <t>AdverseEvent.severity</t>
-  </si>
-  <si>
-    <t>mild | moderate | severe</t>
-  </si>
-  <si>
-    <t>Describes the severity of the adverse event, in relation to the subject. Contrast to AdverseEvent.seriousness - a severe rash might not be serious, but a mild heart problem is.</t>
-  </si>
-  <si>
-    <t>The severity of the adverse event itself, in direct relation to the subject.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/adverse-event-severity|4.0.1</t>
   </si>
   <si>
     <t>AdverseEvent.outcome</t>
@@ -1229,7 +1229,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="57.65234375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="46.62890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="58.41796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -3506,7 +3506,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>202</v>
       </c>
@@ -3519,13 +3519,13 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>78</v>
@@ -3567,11 +3567,13 @@
         <v>78</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>78</v>
@@ -3610,12 +3612,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3623,13 +3625,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
@@ -3641,10 +3643,10 @@
         <v>156</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3673,9 +3675,7 @@
       <c r="X23" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="Y23" t="s" s="2">
-        <v>209</v>
-      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
         <v>210</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
